--- a/files/modify_profile_testcases.xlsx
+++ b/files/modify_profile_testcases.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13812345678</t>
+          <t>13800001001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zhangsan@example.com</t>
+          <t>liming@example.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>所有字段均符合规则</t>
+          <t>昵称使用中文且长度合法；手机号有效且未占用；邮箱格式正确</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>修改成功 提示新邮箱待验证</t>
+          <t>修改成功并发送邮箱验证邮件；新邮箱验证后生效</t>
         </is>
       </c>
     </row>
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alice2024</t>
+          <t>User2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15911112222</t>
+          <t>13900002002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alice_test@example.com</t>
+          <t>user2024@test.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>昵称含字母数字且手机邮箱有效</t>
+          <t>昵称含字母和数字且长度合法；手机号有效且未占用；邮箱格式正确</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>修改成功 提示新邮箱待验证</t>
+          <t>修改成功并提示前往新邮箱完成验证</t>
         </is>
       </c>
     </row>
@@ -535,22 +535,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>李@四</t>
+          <t>张#三</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13712344321</t>
+          <t>13700003003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lisi@example.com</t>
+          <t>zhangsan@sample.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>昵称含特殊符号</t>
+          <t>昵称包含特殊符号#；其他字段均有效</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>修改失败 提示昵称不能含特殊符号</t>
+          <t>校验失败并提示昵称仅支持中文、字母和数字</t>
         </is>
       </c>
     </row>
@@ -572,22 +572,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>王小明</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23812345678</t>
+          <t>12300004004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>wangxm@example.com</t>
+          <t>wangwu@example.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>手机号不是1开头</t>
+          <t>手机号为11位但第二位为2；不符合大陆手机号规则</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>修改失败 提示手机号格式不正确</t>
+          <t>校验失败并提示手机号格式不正确</t>
         </is>
       </c>
     </row>
@@ -609,22 +609,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>李雷雷</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13900001111</t>
+          <t>13600005005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lilei@example.com</t>
+          <t>zhaoliu.example.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>手机号与已有账号重复</t>
+          <t>邮箱缺少@符号；不符合标准邮箱格式</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>修改失败 提示手机号已被使用</t>
+          <t>校验失败并提示请输入正确的邮箱地址</t>
         </is>
       </c>
     </row>
@@ -646,22 +646,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>韩梅梅</t>
+          <t>孙七</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18611112222</t>
+          <t>13500006006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hanmeimei@</t>
+          <t>sunqi@example.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>邮箱格式错误</t>
+          <t>该手机号在系统中已被其他账号绑定</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>修改失败 提示邮箱格式不正确</t>
+          <t>校验失败并提示该手机号已被占用</t>
         </is>
       </c>
     </row>
@@ -683,22 +683,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>阿乐</t>
+          <t>陈晨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13512345678</t>
+          <t>15811112222</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ale@example.com</t>
+          <t>chenchen@example.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>昵称恰为2位合法字符</t>
+          <t>昵称长度恰好为2位；属于合法边界值；其他字段有效</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>修改成功 提示新邮箱待验证</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -720,22 +720,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A23456789012345</t>
+          <t>一二三四五六七八九十一二三四五</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18812345678</t>
+          <t>15933334444</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>user15@example.com</t>
+          <t>boundary15@sample.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>昵称恰为15位合法字符</t>
+          <t>昵称长度恰好为15位；属于合法边界值；其他字段有效</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>修改成功 提示新邮箱待验证</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -757,22 +757,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>昵</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15812345678</t>
+          <t>15122223333</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ni@example.com</t>
+          <t>one@example.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>昵称长度为1位 小于下边界</t>
+          <t>昵称长度仅1位；低于下边界；其他字段有效</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>修改失败 提示昵称长度需为2至15位</t>
+          <t>校验失败并提示昵称长度需为2至15位</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1234567890123456</t>
+          <t>一二三四五六七八九十一二三四五六</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18712345678</t>
+          <t>15244445555</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>len16@example.com</t>
+          <t>length16@example.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>昵称长度为16位 大于上边界</t>
+          <t>昵称长度达16位；超出上边界；其他字段有效</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>修改失败 提示昵称长度需为2至15位</t>
+          <t>校验失败并提示昵称长度需为2至15位</t>
         </is>
       </c>
     </row>

--- a/files/modify_profile_testcases.xlsx
+++ b/files/modify_profile_testcases.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>小明</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13800001001</t>
+          <t>13800000001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>liming@example.com</t>
+          <t>user1@example.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>昵称使用中文且长度合法；手机号有效且未占用；邮箱格式正确</t>
+          <t>昵称手机号邮箱均合法且唯一</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>修改成功并发送邮箱验证邮件；新邮箱验证后生效</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>User2024</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13900002002</t>
+          <t>13800000002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>user2024@test.com</t>
+          <t>user2@example.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>昵称含字母和数字且长度合法；手机号有效且未占用；邮箱格式正确</t>
+          <t>昵称字母手机号邮箱均合法</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>修改成功并提示前往新邮箱完成验证</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -535,32 +535,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>张#三</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13700003003</t>
+          <t>13800000003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>zhangsan@sample.com</t>
+          <t>user3@example.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>昵称包含特殊符号#；其他字段均有效</t>
+          <t>昵称长度2位合法边界</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>校验失败并提示昵称仅支持中文、字母和数字</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -572,32 +572,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>abcdefghijklmno</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12300004004</t>
+          <t>13800000004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>wangwu@example.com</t>
+          <t>user4@example.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>手机号为11位但第二位为2；不符合大陆手机号规则</t>
+          <t>昵称长度15位合法边界</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>校验失败并提示手机号格式不正确</t>
+          <t>修改成功并发送邮箱验证邮件</t>
         </is>
       </c>
     </row>
@@ -609,32 +609,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13600005005</t>
+          <t>13800000005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>zhaoliu.example.com</t>
+          <t>user5@example.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>邮箱缺少@符号；不符合标准邮箱格式</t>
+          <t>昵称长度1位非法边界</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>校验失败并提示请输入正确的邮箱地址</t>
+          <t>提示昵称长度需为2到15位</t>
         </is>
       </c>
     </row>
@@ -646,32 +646,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>孙七</t>
+          <t>abcdefghijklmnop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13500006006</t>
+          <t>13800000006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sunqi@example.com</t>
+          <t>user6@example.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>该手机号在系统中已被其他账号绑定</t>
+          <t>昵称长度16位非法边界</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>校验失败并提示该手机号已被占用</t>
+          <t>提示昵称长度需为2到15位</t>
         </is>
       </c>
     </row>
@@ -683,32 +683,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>陈晨</t>
+          <t>测试@</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15811112222</t>
+          <t>13800000007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>chenchen@example.com</t>
+          <t>user7@example.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>昵称长度恰好为2位；属于合法边界值；其他字段有效</t>
+          <t>昵称含特殊符号@</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>健壮边界值（合法边界）</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>修改成功并发送邮箱验证邮件</t>
+          <t>提示昵称仅支持中文字母数字</t>
         </is>
       </c>
     </row>
@@ -720,32 +720,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>一二三四五六七八九十一二三四五</t>
+          <t>用户123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15933334444</t>
+          <t>1380000000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>boundary15@sample.com</t>
+          <t>user8@example.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>昵称长度恰好为15位；属于合法边界值；其他字段有效</t>
+          <t>手机号10位</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>健壮边界值（合法边界）</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>修改成功并发送邮箱验证邮件</t>
+          <t>提示手机号需为1开头11位数字</t>
         </is>
       </c>
     </row>
@@ -757,32 +757,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>用户ABC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15122223333</t>
+          <t>23800000001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>one@example.com</t>
+          <t>userexample.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>昵称长度仅1位；低于下边界；其他字段有效</t>
+          <t>手机号不以1开头且邮箱缺少@</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>健壮边界值（非法边界）</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>校验失败并提示昵称长度需为2至15位</t>
+          <t>提示手机号格式错误和邮箱格式错误</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>一二三四五六七八九十一二三四五六</t>
+          <t>用户XYZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15244445555</t>
+          <t>13700000000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>length16@example.com</t>
+          <t>user@example</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>昵称长度达16位；超出上边界；其他字段有效</t>
+          <t>手机号已被占用且邮箱缺少顶级域名</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>健壮边界值（非法边界）</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>校验失败并提示昵称长度需为2至15位</t>
+          <t>提示手机号已注册和邮箱格式错误</t>
         </is>
       </c>
     </row>
